--- a/aircraft/reports/manufacturer/Embraer/aircraft-type-pie-chart.xlsx
+++ b/aircraft/reports/manufacturer/Embraer/aircraft-type-pie-chart.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M337"/>
+  <dimension ref="A1:M338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20990,6 +20990,67 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B338" t="n">
+        <v>15552</v>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Abingdon</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>KL1130</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>ORK</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>PH-EZG</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>19000315</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>ERJ-190STD</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Embraer</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
